--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -10579,7 +10579,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆两江新区交付中心</t>
+          <t>小鹏汽车重庆二郎销售中心</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>重庆市九龙坡区石新路172号附2号</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆二郎销售中心</t>
+          <t>小鹏汽车重庆两江新区交付中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区石新路172号附2号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>东莞世奥</t>
+          <t>东莞捷世丰</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>广东省东莞市南城区莞太大道石鼓路段</t>
+          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>东莞捷世丰</t>
+          <t>东莞世奥</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
+          <t>广东省东莞市南城区莞太大道石鼓路段</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>佛山广物君奥</t>
+          <t>佛山世锦</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区佛山大道中路83号</t>
+          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>佛山世锦</t>
+          <t>佛山广物君奥</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
+          <t>广东省佛山市禅城区佛山大道中路83号</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12083,14 +12083,14 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12186,22 +12186,22 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12223,17 +12223,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
@@ -12255,17 +12255,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
@@ -12287,17 +12287,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12307,29 +12307,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州南服务中心</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -10953,7 +10953,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>东莞捷世丰</t>
+          <t>东莞世奥</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
+          <t>广东省东莞市南城区莞太大道石鼓路段</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>东莞世奥</t>
+          <t>东莞捷世丰</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>广东省东莞市南城区莞太大道石鼓路段</t>
+          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>广东广物金盈汽车贸易有限公司</t>
+          <t>广州南菱奥申</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区机场路898号</t>
+          <t>广东省广州市白云区广花一路136号</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>广州南菱奥申</t>
+          <t>广东广物金盈汽车贸易有限公司</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区广花一路136号</t>
+          <t>广东省广州市白云区机场路898号</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12083,14 +12083,14 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
@@ -12191,17 +12191,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
@@ -12260,12 +12260,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12275,14 +12275,14 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -12292,12 +12292,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
@@ -12442,22 +12442,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩万象天地新能源空间</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩印象城新能源空间</t>
+          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12467,29 +12467,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>南昌红谷滩万象天地新能源空间</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
+          <t>南昌红谷滩印象城新能源空间</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -10579,7 +10579,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆二郎销售中心</t>
+          <t>小鹏汽车重庆两江新区交付中心</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区石新路172号附2号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆两江新区交付中心</t>
+          <t>小鹏汽车重庆二郎销售中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>重庆市九龙坡区石新路172号附2号</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>广州南菱奥申</t>
+          <t>广东广物金盈汽车贸易有限公司</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区广花一路136号</t>
+          <t>广东省广州市白云区机场路898号</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>广东广物金盈汽车贸易有限公司</t>
+          <t>广州南菱奥申</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区机场路898号</t>
+          <t>广东省广州市白云区广花一路136号</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12083,14 +12083,14 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12196,12 +12196,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12228,12 +12228,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
@@ -12255,17 +12255,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12275,29 +12275,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
@@ -12442,22 +12442,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>南昌红谷滩万象天地新能源空间</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
+          <t>南昌红谷滩印象城新能源空间</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12467,29 +12467,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩万象天地新能源空间</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩印象城新能源空间</t>
+          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -10953,7 +10953,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>东莞世奥</t>
+          <t>东莞捷世丰</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>广东省东莞市南城区莞太大道石鼓路段</t>
+          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>东莞捷世丰</t>
+          <t>东莞世奥</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
+          <t>广东省东莞市南城区莞太大道石鼓路段</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>福建华奥</t>
+          <t>福建润通</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇良安路20号</t>
+          <t>福建省福州市仓山区高仕路2号</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>福建润通</t>
+          <t>福建华奥</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区高仕路2号</t>
+          <t>福建省福州市闽侯县尚干镇良安路20号</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12051,29 +12051,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12083,29 +12083,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12196,12 +12196,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12223,17 +12223,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12255,17 +12255,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
@@ -12287,17 +12287,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12307,29 +12307,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州南服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12442,22 +12442,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩万象天地新能源空间</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩印象城新能源空间</t>
+          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12467,29 +12467,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>南昌红谷滩万象天地新能源空间</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
+          <t>南昌红谷滩印象城新能源空间</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -10579,7 +10579,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆两江新区交付中心</t>
+          <t>小鹏汽车重庆二郎销售中心</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>重庆市九龙坡区石新路172号附2号</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆二郎销售中心</t>
+          <t>小鹏汽车重庆两江新区交付中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区石新路172号附2号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12051,29 +12051,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
@@ -12164,12 +12164,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12196,12 +12196,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12223,17 +12223,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12243,29 +12243,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
@@ -12287,17 +12287,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12307,29 +12307,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州南服务中心</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -10579,7 +10579,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆二郎销售中心</t>
+          <t>小鹏汽车重庆两江新区交付中心</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区石新路172号附2号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆两江新区交付中心</t>
+          <t>小鹏汽车重庆二郎销售中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>重庆市九龙坡区石新路172号附2号</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>东莞捷世丰</t>
+          <t>东莞世奥</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
+          <t>广东省东莞市南城区莞太大道石鼓路段</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>东莞世奥</t>
+          <t>东莞捷世丰</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>广东省东莞市南城区莞太大道石鼓路段</t>
+          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>佛山世锦</t>
+          <t>佛山广物君奥</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
+          <t>广东省佛山市禅城区佛山大道中路83号</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>佛山广物君奥</t>
+          <t>佛山世锦</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区佛山大道中路83号</t>
+          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12019,29 +12019,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
@@ -12191,17 +12191,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12223,17 +12223,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12243,29 +12243,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12287,17 +12287,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12307,29 +12307,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州南服务中心</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12442,22 +12442,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>南昌红谷滩万象天地新能源空间</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
+          <t>南昌红谷滩印象城新能源空间</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12467,29 +12467,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩万象天地新能源空间</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩印象城新能源空间</t>
+          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -10579,7 +10579,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆两江新区交付中心</t>
+          <t>小鹏汽车重庆二郎销售中心</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
+          <t>重庆市九龙坡区石新路172号附2号</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆二郎销售中心</t>
+          <t>小鹏汽车重庆两江新区交付中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>重庆市九龙坡区石新路172号附2号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>佛山广物君奥</t>
+          <t>佛山世锦</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区佛山大道中路83号</t>
+          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>佛山世锦</t>
+          <t>佛山广物君奥</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
+          <t>广东省佛山市禅城区佛山大道中路83号</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>福建润通</t>
+          <t>福建华奥</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区高仕路2号</t>
+          <t>福建省福州市闽侯县尚干镇良安路20号</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>福建华奥</t>
+          <t>福建润通</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇良安路20号</t>
+          <t>福建省福州市仓山区高仕路2号</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12019,14 +12019,14 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -12036,12 +12036,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12191,17 +12191,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
@@ -12250,22 +12250,22 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
@@ -12287,17 +12287,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12307,29 +12307,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州南服务中心</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12442,22 +12442,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩万象天地新能源空间</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩印象城新能源空间</t>
+          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12467,29 +12467,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>南昌红谷滩万象天地新能源空间</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
+          <t>南昌红谷滩印象城新能源空间</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -11081,7 +11081,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>广东广物金盈汽车贸易有限公司</t>
+          <t>广州南菱奥申</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区机场路898号</t>
+          <t>广东省广州市白云区广花一路136号</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>广州南菱奥申</t>
+          <t>广东广物金盈汽车贸易有限公司</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区广花一路136号</t>
+          <t>广东省广州市白云区机场路898号</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>福建华奥</t>
+          <t>福建润通</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇良安路20号</t>
+          <t>福建省福州市仓山区高仕路2号</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>福建润通</t>
+          <t>福建华奥</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区高仕路2号</t>
+          <t>福建省福州市闽侯县尚干镇良安路20号</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
@@ -12100,12 +12100,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12132,12 +12132,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
@@ -12191,17 +12191,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12211,14 +12211,14 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -12228,12 +12228,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12243,14 +12243,14 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
@@ -12287,17 +12287,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12307,29 +12307,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小鹏汽车泉州南服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州南服务中心</t>
+          <t>广州（汕头）交付中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>广州科学城交付中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>广州（汕头）交付中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>广州科学城交付中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12442,22 +12442,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>南昌红谷滩万象天地新能源空间</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
+          <t>南昌红谷滩印象城新能源空间</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12467,29 +12467,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩万象天地新能源空间</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩印象城新能源空间</t>
+          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -11081,7 +11081,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>广州南菱奥申</t>
+          <t>广东广物金盈汽车贸易有限公司</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区广花一路136号</t>
+          <t>广东省广州市白云区机场路898号</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>广东广物金盈汽车贸易有限公司</t>
+          <t>广州南菱奥申</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区机场路898号</t>
+          <t>广东省广州市白云区广花一路136号</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>福建润通</t>
+          <t>福建华奥</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区高仕路2号</t>
+          <t>福建省福州市闽侯县尚干镇良安路20号</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>福建华奥</t>
+          <t>福建润通</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇良安路20号</t>
+          <t>福建省福州市仓山区高仕路2号</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12186,7 +12186,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12211,14 +12211,14 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -12228,12 +12228,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
@@ -12255,17 +12255,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12442,22 +12442,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩万象天地新能源空间</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩印象城新能源空间</t>
+          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12467,29 +12467,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>南昌红谷滩万象天地新能源空间</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市余杭区闲林服务中心</t>
+          <t>南昌红谷滩印象城新能源空间</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -10953,7 +10953,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>东莞世奥</t>
+          <t>东莞捷世丰</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>广东省东莞市南城区莞太大道石鼓路段</t>
+          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>东莞捷世丰</t>
+          <t>东莞世奥</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>东莞市市辖区环常西路桥梓路段额头工业区3号</t>
+          <t>广东省东莞市南城区莞太大道石鼓路段</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>佛山世锦</t>
+          <t>佛山广物君奥</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
+          <t>广东省佛山市禅城区佛山大道中路83号</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>佛山广物君奥</t>
+          <t>佛山世锦</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区佛山大道中路83号</t>
+          <t>广东省佛山市顺德区大良广珠公路新松路段30号</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>广东广物金盈汽车贸易有限公司</t>
+          <t>广州南菱奥申</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区机场路898号</t>
+          <t>广东省广州市白云区广花一路136号</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>广州南菱奥申</t>
+          <t>广东广物金盈汽车贸易有限公司</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>广东省广州市白云区广花一路136号</t>
+          <t>广东省广州市白云区机场路898号</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
@@ -12223,17 +12223,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12260,12 +12260,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12287,17 +12287,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260622_vs_20260629.xlsx
@@ -11273,7 +11273,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>福建华奥</t>
+          <t>福建润通</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县尚干镇良安路20号</t>
+          <t>福建省福州市仓山区高仕路2号</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>福建润通</t>
+          <t>福建华奥</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区高仕路2号</t>
+          <t>福建省福州市闽侯县尚干镇良安路20号</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
+          <t>小鹏汽车重庆礼嘉服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
+          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
         </is>
       </c>
     </row>
@@ -12068,12 +12068,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口</t>
+          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
         </is>
       </c>
     </row>
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12115,29 +12115,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号1楼108房 → 广州市白云区白云大道北1399号</t>
+          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
+          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
         </is>
       </c>
     </row>
@@ -12164,12 +12164,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12179,29 +12179,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
+          <t>浙江省宁波市江北区中官新路555号 → 浙江省宁波市江北区中官新路555号18#-1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市天河区美林天地汽车体验店</t>
+          <t>小鹏汽车常德大道销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>黄埔大道东663号 → 黄埔大道东657号1F003-005、2F001-004铺</t>
+          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -12223,17 +12223,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆礼嘉服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼环北路10号普洛斯（重庆）物流园2期礼嘉园区B3栋小鹏汽车 → 重庆市两江新区康美街道嘉材路26号2楼</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区329国道88号</t>
         </is>
       </c>
     </row>
@@ -12255,17 +12255,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道40号（湘西北汽车城内） → 常德市武陵区常德大道龙港路1088号（湘西北汽车城内）</t>
+          <t>广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12287,17 +12287,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心</t>
+          <t>小鹏汽车张家港曼巴特购物广场销售展厅</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售中心 → 武陵区常德大道1888号</t>
+          <t>张家港曼巴特 → 江苏省张家港市杨舍镇河西路88号</t>
         </is>
       </c>
     </row>
